--- a/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MAR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072322E3-A1DC-4A0C-93E6-D997B338DE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB5CAA5-73F3-4F8B-ABA1-8175666141EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
